--- a/JHBI_Revenue_Model.xlsx
+++ b/JHBI_Revenue_Model.xlsx
@@ -1801,8 +1801,8 @@
         <v>60</v>
       </c>
       <c r="B7" s="29" t="n">
-        <f aca="false">1-B5</f>
-        <v>-1659</v>
+        <f aca="false">1-B6</f>
+        <v>0.56</v>
       </c>
       <c r="G7" s="27" t="s">
         <v>61</v>
@@ -2143,19 +2143,19 @@
       </c>
       <c r="B30" s="38" t="n">
         <f aca="false">Assumptions!B22*(1-$B$7)</f>
-        <v>8300000</v>
+        <v>2200</v>
       </c>
       <c r="C30" s="38" t="n">
         <f aca="false">Assumptions!C22*(1-$B$7)</f>
-        <v>13280000</v>
+        <v>3520</v>
       </c>
       <c r="D30" s="38" t="n">
         <f aca="false">Assumptions!D22*(1-$B$7)</f>
-        <v>24900000</v>
+        <v>6600</v>
       </c>
       <c r="E30" s="38" t="n">
         <f aca="false">Assumptions!E22*(1-$B$7)</f>
-        <v>41500000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2165,19 +2165,19 @@
       </c>
       <c r="B31" s="40" t="n">
         <f aca="false">Assumptions!B23*(1-$B$7)</f>
-        <v>13280000</v>
+        <v>3520</v>
       </c>
       <c r="C31" s="40" t="n">
         <f aca="false">Assumptions!C23*(1-$B$7)</f>
-        <v>19920000</v>
+        <v>5280</v>
       </c>
       <c r="D31" s="40" t="n">
         <f aca="false">Assumptions!D23*(1-$B$7)</f>
-        <v>36520000</v>
+        <v>9680</v>
       </c>
       <c r="E31" s="40" t="n">
         <f aca="false">Assumptions!E23*(1-$B$7)</f>
-        <v>58100000</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2187,19 +2187,19 @@
       </c>
       <c r="B32" s="38" t="n">
         <f aca="false">Assumptions!B24*(1-$B$7)</f>
-        <v>9960000</v>
+        <v>2640</v>
       </c>
       <c r="C32" s="38" t="n">
         <f aca="false">Assumptions!C24*(1-$B$7)</f>
-        <v>16600000</v>
+        <v>4400</v>
       </c>
       <c r="D32" s="38" t="n">
         <f aca="false">Assumptions!D24*(1-$B$7)</f>
-        <v>29880000</v>
+        <v>7920</v>
       </c>
       <c r="E32" s="38" t="n">
         <f aca="false">Assumptions!E24*(1-$B$7)</f>
-        <v>46480000</v>
+        <v>12320</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2209,19 +2209,19 @@
       </c>
       <c r="B33" s="40" t="n">
         <f aca="false">Assumptions!B25*(1-$B$7)</f>
-        <v>13280000</v>
+        <v>3520</v>
       </c>
       <c r="C33" s="40" t="n">
         <f aca="false">Assumptions!C25*(1-$B$7)</f>
-        <v>19920000</v>
+        <v>5280</v>
       </c>
       <c r="D33" s="40" t="n">
         <f aca="false">Assumptions!D25*(1-$B$7)</f>
-        <v>33200000</v>
+        <v>8800</v>
       </c>
       <c r="E33" s="40" t="n">
         <f aca="false">Assumptions!E25*(1-$B$7)</f>
-        <v>49800000</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2231,19 +2231,19 @@
       </c>
       <c r="B34" s="38" t="n">
         <f aca="false">Assumptions!B26*(1-$B$7)</f>
-        <v>13280000</v>
+        <v>3520</v>
       </c>
       <c r="C34" s="38" t="n">
         <f aca="false">Assumptions!C26*(1-$B$7)</f>
-        <v>24900000</v>
+        <v>6600</v>
       </c>
       <c r="D34" s="38" t="n">
         <f aca="false">Assumptions!D26*(1-$B$7)</f>
-        <v>41500000</v>
+        <v>11000</v>
       </c>
       <c r="E34" s="38" t="n">
         <f aca="false">Assumptions!E26*(1-$B$7)</f>
-        <v>66400000</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/JHBI_Revenue_Model.xlsx
+++ b/JHBI_Revenue_Model.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Oct–Dec 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">↑ $1M crossed Q4 FY27 (Apr–Jun 2027)</t>
+    <t xml:space="preserve">↑ $1M crossed Q1 FY28 (Jul–Sep 2027)  |  Zelle base = 260 FIs (15.7% of 1,660)  |  8% annual churn corrected</t>
   </si>
   <si>
     <t xml:space="preserve">KEY ASSUMPTIONS DRIVING THE MODEL</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Zelle Penetration (% of FIs)</t>
   </si>
   <si>
-    <t xml:space="preserve">Est. ~35% of JH FIs have JHA PayCenter / Zelle enabled</t>
+    <t xml:space="preserve">260 of ~1,660 JH core FIs currently Zelle-enabled via JHA PayCenter</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Subscription Churn Rate</t>
@@ -285,7 +285,7 @@
     <t xml:space="preserve">Zelle Memo Intelligence</t>
   </si>
   <si>
-    <t xml:space="preserve">Zelle-enabled FIs only (~35% of base)</t>
+    <t xml:space="preserve">Zelle-enabled FIs only (260 currently; ~15.7% of base)</t>
   </si>
   <si>
     <t xml:space="preserve">Churn Sentinel</t>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">'Revenue Model'!E8</f>
-        <v>116400</v>
+        <v>48500</v>
       </c>
       <c r="D8" s="8" t="n">
         <f aca="false">'Revenue Model'!E13</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H8" s="9" t="n">
         <f aca="false">'Revenue Model'!E32</f>
-        <v>116400</v>
+        <v>48500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">'Revenue Model'!F8</f>
-        <v>203700</v>
+        <v>87300</v>
       </c>
       <c r="D9" s="12" t="n">
         <f aca="false">'Revenue Model'!F13</f>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H9" s="13" t="n">
         <f aca="false">'Revenue Model'!F32</f>
-        <v>409200</v>
+        <v>292800</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1424,11 +1424,11 @@
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">'Revenue Model'!G8</f>
-        <v>281300</v>
+        <v>126100</v>
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">'Revenue Model'!G13</f>
-        <v>369900</v>
+        <v>383600</v>
       </c>
       <c r="E10" s="8" t="n">
         <f aca="false">'Revenue Model'!G18</f>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="H10" s="9" t="n">
         <f aca="false">'Revenue Model'!G32</f>
-        <v>762200</v>
+        <v>620700</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1456,15 +1456,15 @@
       </c>
       <c r="C11" s="16" t="n">
         <f aca="false">'Revenue Model'!H8</f>
-        <v>329800</v>
+        <v>164900</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">'Revenue Model'!H13</f>
-        <v>506900</v>
+        <v>534300</v>
       </c>
       <c r="E11" s="16" t="n">
         <f aca="false">'Revenue Model'!H18</f>
-        <v>199800</v>
+        <v>210900</v>
       </c>
       <c r="F11" s="16" t="n">
         <f aca="false">'Revenue Model'!H23</f>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">'Revenue Model'!H32</f>
-        <v>1036500</v>
+        <v>910100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1488,15 +1488,15 @@
       </c>
       <c r="C12" s="8" t="n">
         <f aca="false">'Revenue Model'!I8</f>
-        <v>368600</v>
+        <v>194000</v>
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">'Revenue Model'!I13</f>
-        <v>602800</v>
+        <v>657600</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">'Revenue Model'!I18</f>
-        <v>266400</v>
+        <v>299700</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">'Revenue Model'!I23</f>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="H12" s="9" t="n">
         <f aca="false">'Revenue Model'!I32</f>
-        <v>1333000</v>
+        <v>1246500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1520,19 +1520,19 @@
       </c>
       <c r="C13" s="12" t="n">
         <f aca="false">'Revenue Model'!J8</f>
-        <v>397700</v>
+        <v>223100</v>
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">'Revenue Model'!J13</f>
-        <v>657600</v>
+        <v>753500</v>
       </c>
       <c r="E13" s="12" t="n">
         <f aca="false">'Revenue Model'!J18</f>
-        <v>321900</v>
+        <v>366300</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">'Revenue Model'!J23</f>
-        <v>163200</v>
+        <v>176800</v>
       </c>
       <c r="G13" s="12" t="n">
         <f aca="false">'Revenue Model'!J28</f>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">'Revenue Model'!J32</f>
-        <v>1658000</v>
+        <v>1637300</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1824,7 +1824,7 @@
         <v>64</v>
       </c>
       <c r="B9" s="28" t="n">
-        <v>0.35</v>
+        <v>0.157</v>
       </c>
       <c r="G9" s="27" t="s">
         <v>65</v>
@@ -1881,16 +1881,16 @@
         <v>500</v>
       </c>
       <c r="C14" s="30" t="n">
-        <f aca="false">ROUND(B14*$B$5,0)</f>
-        <v>830000</v>
+        <f aca="false">ROUND(B14*$B$6,0)</f>
+        <v>220</v>
       </c>
       <c r="D14" s="30" t="n">
         <f aca="false">B14-C14</f>
-        <v>-829500</v>
+        <v>280</v>
       </c>
       <c r="E14" s="30" t="n">
-        <f aca="false">ROUND(B14*$B$8,0)</f>
-        <v>60</v>
+        <f aca="false">ROUND(B14*$B$9,0)</f>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1901,16 +1901,16 @@
         <v>800</v>
       </c>
       <c r="C15" s="31" t="n">
-        <f aca="false">ROUND(B15*$B$5,0)</f>
-        <v>1328000</v>
+        <f aca="false">ROUND(B15*$B$6,0)</f>
+        <v>352</v>
       </c>
       <c r="D15" s="31" t="n">
         <f aca="false">B15-C15</f>
-        <v>-1327200</v>
+        <v>448</v>
       </c>
       <c r="E15" s="31" t="n">
-        <f aca="false">ROUND(B15*$B$8,0)</f>
-        <v>96</v>
+        <f aca="false">ROUND(B15*$B$9,0)</f>
+        <v>126</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1921,16 +1921,16 @@
         <v>280</v>
       </c>
       <c r="C16" s="30" t="n">
-        <f aca="false">ROUND(B16*$B$5,0)</f>
-        <v>464800</v>
+        <f aca="false">ROUND(B16*$B$6,0)</f>
+        <v>123</v>
       </c>
       <c r="D16" s="30" t="n">
         <f aca="false">B16-C16</f>
-        <v>-464520</v>
+        <v>157</v>
       </c>
       <c r="E16" s="30" t="n">
-        <f aca="false">ROUND(B16*$B$8,0)</f>
-        <v>34</v>
+        <f aca="false">ROUND(B16*$B$9,0)</f>
+        <v>44</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1941,16 +1941,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="31" t="n">
-        <f aca="false">ROUND(B17*$B$5,0)</f>
-        <v>132800</v>
+        <f aca="false">ROUND(B17*$B$6,0)</f>
+        <v>35</v>
       </c>
       <c r="D17" s="31" t="n">
         <f aca="false">B17-C17</f>
-        <v>-132720</v>
+        <v>45</v>
       </c>
       <c r="E17" s="31" t="n">
-        <f aca="false">ROUND(B17*$B$8,0)</f>
-        <v>10</v>
+        <f aca="false">ROUND(B17*$B$9,0)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1963,15 +1963,15 @@
       </c>
       <c r="C18" s="32" t="n">
         <f aca="false">SUM(C14:C17)</f>
-        <v>2755600</v>
+        <v>730</v>
       </c>
       <c r="D18" s="32" t="n">
         <f aca="false">SUM(D14:D17)</f>
-        <v>-2753940</v>
+        <v>930</v>
       </c>
       <c r="E18" s="32" t="n">
         <f aca="false">SUM(E14:E17)</f>
-        <v>200</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2542,22 +2542,22 @@
         <v>0</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2572,32 +2572,32 @@
         <v>0</v>
       </c>
       <c r="D7" s="31" t="n">
-        <f aca="false">ROUND(C7*(1-Assumptions!$B$9/4)+D6,0)</f>
+        <f aca="false">ROUND(C7*(1-Assumptions!$B$10/4)+D6,0)</f>
         <v>0</v>
       </c>
       <c r="E7" s="31" t="n">
-        <f aca="false">ROUND(D7*(1-Assumptions!$B$9/4)+E6,0)</f>
-        <v>12</v>
+        <f aca="false">ROUND(D7*(1-Assumptions!$B$10/4)+E6,0)</f>
+        <v>5</v>
       </c>
       <c r="F7" s="31" t="n">
-        <f aca="false">ROUND(E7*(1-Assumptions!$B$9/4)+F6,0)</f>
-        <v>21</v>
+        <f aca="false">ROUND(E7*(1-Assumptions!$B$10/4)+F6,0)</f>
+        <v>9</v>
       </c>
       <c r="G7" s="31" t="n">
-        <f aca="false">ROUND(F7*(1-Assumptions!$B$9/4)+G6,0)</f>
-        <v>29</v>
+        <f aca="false">ROUND(F7*(1-Assumptions!$B$10/4)+G6,0)</f>
+        <v>13</v>
       </c>
       <c r="H7" s="31" t="n">
-        <f aca="false">ROUND(G7*(1-Assumptions!$B$9/4)+H6,0)</f>
-        <v>34</v>
+        <f aca="false">ROUND(G7*(1-Assumptions!$B$10/4)+H6,0)</f>
+        <v>17</v>
       </c>
       <c r="I7" s="31" t="n">
-        <f aca="false">ROUND(H7*(1-Assumptions!$B$9/4)+I6,0)</f>
-        <v>38</v>
+        <f aca="false">ROUND(H7*(1-Assumptions!$B$10/4)+I6,0)</f>
+        <v>20</v>
       </c>
       <c r="J7" s="31" t="n">
-        <f aca="false">ROUND(I7*(1-Assumptions!$B$9/4)+J6,0)</f>
-        <v>41</v>
+        <f aca="false">ROUND(I7*(1-Assumptions!$B$10/4)+J6,0)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2617,27 +2617,27 @@
       </c>
       <c r="E8" s="41" t="n">
         <f aca="false">ROUND(E7*Assumptions!$B$39,0)</f>
-        <v>116400</v>
+        <v>48500</v>
       </c>
       <c r="F8" s="41" t="n">
         <f aca="false">ROUND(F7*Assumptions!$B$39,0)</f>
-        <v>203700</v>
+        <v>87300</v>
       </c>
       <c r="G8" s="41" t="n">
         <f aca="false">ROUND(G7*Assumptions!$B$39,0)</f>
-        <v>281300</v>
+        <v>126100</v>
       </c>
       <c r="H8" s="41" t="n">
         <f aca="false">ROUND(H7*Assumptions!$B$39,0)</f>
-        <v>329800</v>
+        <v>164900</v>
       </c>
       <c r="I8" s="41" t="n">
         <f aca="false">ROUND(I7*Assumptions!$B$39,0)</f>
-        <v>368600</v>
+        <v>194000</v>
       </c>
       <c r="J8" s="41" t="n">
         <f aca="false">ROUND(J7*Assumptions!$B$39,0)</f>
-        <v>397700</v>
+        <v>223100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2699,32 +2699,32 @@
         <v>0</v>
       </c>
       <c r="D12" s="31" t="n">
-        <f aca="false">ROUND(C12*(1-Assumptions!$B$9/4)+D11,0)</f>
+        <f aca="false">ROUND(C12*(1-Assumptions!$B$10/4)+D11,0)</f>
         <v>0</v>
       </c>
       <c r="E12" s="31" t="n">
-        <f aca="false">ROUND(D12*(1-Assumptions!$B$9/4)+E11,0)</f>
+        <f aca="false">ROUND(D12*(1-Assumptions!$B$10/4)+E11,0)</f>
         <v>0</v>
       </c>
       <c r="F12" s="31" t="n">
-        <f aca="false">ROUND(E12*(1-Assumptions!$B$9/4)+F11,0)</f>
+        <f aca="false">ROUND(E12*(1-Assumptions!$B$10/4)+F11,0)</f>
         <v>15</v>
       </c>
       <c r="G12" s="31" t="n">
-        <f aca="false">ROUND(F12*(1-Assumptions!$B$9/4)+G11,0)</f>
-        <v>27</v>
+        <f aca="false">ROUND(F12*(1-Assumptions!$B$10/4)+G11,0)</f>
+        <v>28</v>
       </c>
       <c r="H12" s="31" t="n">
-        <f aca="false">ROUND(G12*(1-Assumptions!$B$9/4)+H11,0)</f>
-        <v>37</v>
+        <f aca="false">ROUND(G12*(1-Assumptions!$B$10/4)+H11,0)</f>
+        <v>39</v>
       </c>
       <c r="I12" s="31" t="n">
-        <f aca="false">ROUND(H12*(1-Assumptions!$B$9/4)+I11,0)</f>
-        <v>44</v>
+        <f aca="false">ROUND(H12*(1-Assumptions!$B$10/4)+I11,0)</f>
+        <v>48</v>
       </c>
       <c r="J12" s="31" t="n">
-        <f aca="false">ROUND(I12*(1-Assumptions!$B$9/4)+J11,0)</f>
-        <v>48</v>
+        <f aca="false">ROUND(I12*(1-Assumptions!$B$10/4)+J11,0)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2752,19 +2752,19 @@
       </c>
       <c r="G13" s="41" t="n">
         <f aca="false">ROUND(G12*Assumptions!$B$40,0)</f>
-        <v>369900</v>
+        <v>383600</v>
       </c>
       <c r="H13" s="41" t="n">
         <f aca="false">ROUND(H12*Assumptions!$B$40,0)</f>
-        <v>506900</v>
+        <v>534300</v>
       </c>
       <c r="I13" s="41" t="n">
         <f aca="false">ROUND(I12*Assumptions!$B$40,0)</f>
-        <v>602800</v>
+        <v>657600</v>
       </c>
       <c r="J13" s="41" t="n">
         <f aca="false">ROUND(J12*Assumptions!$B$40,0)</f>
-        <v>657600</v>
+        <v>753500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2826,32 +2826,32 @@
         <v>0</v>
       </c>
       <c r="D17" s="31" t="n">
-        <f aca="false">ROUND(C17*(1-Assumptions!$B$9/4)+D16,0)</f>
+        <f aca="false">ROUND(C17*(1-Assumptions!$B$10/4)+D16,0)</f>
         <v>0</v>
       </c>
       <c r="E17" s="31" t="n">
-        <f aca="false">ROUND(D17*(1-Assumptions!$B$9/4)+E16,0)</f>
+        <f aca="false">ROUND(D17*(1-Assumptions!$B$10/4)+E16,0)</f>
         <v>0</v>
       </c>
       <c r="F17" s="31" t="n">
-        <f aca="false">ROUND(E17*(1-Assumptions!$B$9/4)+F16,0)</f>
+        <f aca="false">ROUND(E17*(1-Assumptions!$B$10/4)+F16,0)</f>
         <v>0</v>
       </c>
       <c r="G17" s="31" t="n">
-        <f aca="false">ROUND(F17*(1-Assumptions!$B$9/4)+G16,0)</f>
+        <f aca="false">ROUND(F17*(1-Assumptions!$B$10/4)+G16,0)</f>
         <v>10</v>
       </c>
       <c r="H17" s="31" t="n">
-        <f aca="false">ROUND(G17*(1-Assumptions!$B$9/4)+H16,0)</f>
-        <v>18</v>
+        <f aca="false">ROUND(G17*(1-Assumptions!$B$10/4)+H16,0)</f>
+        <v>19</v>
       </c>
       <c r="I17" s="31" t="n">
-        <f aca="false">ROUND(H17*(1-Assumptions!$B$9/4)+I16,0)</f>
-        <v>24</v>
+        <f aca="false">ROUND(H17*(1-Assumptions!$B$10/4)+I16,0)</f>
+        <v>27</v>
       </c>
       <c r="J17" s="31" t="n">
-        <f aca="false">ROUND(I17*(1-Assumptions!$B$9/4)+J16,0)</f>
-        <v>29</v>
+        <f aca="false">ROUND(I17*(1-Assumptions!$B$10/4)+J16,0)</f>
+        <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2883,15 +2883,15 @@
       </c>
       <c r="H18" s="41" t="n">
         <f aca="false">ROUND(H17*Assumptions!$B$41,0)</f>
-        <v>199800</v>
+        <v>210900</v>
       </c>
       <c r="I18" s="41" t="n">
         <f aca="false">ROUND(I17*Assumptions!$B$41,0)</f>
-        <v>266400</v>
+        <v>299700</v>
       </c>
       <c r="J18" s="41" t="n">
         <f aca="false">ROUND(J17*Assumptions!$B$41,0)</f>
-        <v>321900</v>
+        <v>366300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2953,32 +2953,32 @@
         <v>0</v>
       </c>
       <c r="D22" s="31" t="n">
-        <f aca="false">ROUND(C22*(1-Assumptions!$B$9/4)+D21,0)</f>
+        <f aca="false">ROUND(C22*(1-Assumptions!$B$10/4)+D21,0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="31" t="n">
-        <f aca="false">ROUND(D22*(1-Assumptions!$B$9/4)+E21,0)</f>
+        <f aca="false">ROUND(D22*(1-Assumptions!$B$10/4)+E21,0)</f>
         <v>0</v>
       </c>
       <c r="F22" s="31" t="n">
-        <f aca="false">ROUND(E22*(1-Assumptions!$B$9/4)+F21,0)</f>
+        <f aca="false">ROUND(E22*(1-Assumptions!$B$10/4)+F21,0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="31" t="n">
-        <f aca="false">ROUND(F22*(1-Assumptions!$B$9/4)+G21,0)</f>
+        <f aca="false">ROUND(F22*(1-Assumptions!$B$10/4)+G21,0)</f>
         <v>0</v>
       </c>
       <c r="H22" s="31" t="n">
-        <f aca="false">ROUND(G22*(1-Assumptions!$B$9/4)+H21,0)</f>
+        <f aca="false">ROUND(G22*(1-Assumptions!$B$10/4)+H21,0)</f>
         <v>0</v>
       </c>
       <c r="I22" s="31" t="n">
-        <f aca="false">ROUND(H22*(1-Assumptions!$B$9/4)+I21,0)</f>
+        <f aca="false">ROUND(H22*(1-Assumptions!$B$10/4)+I21,0)</f>
         <v>7</v>
       </c>
       <c r="J22" s="31" t="n">
-        <f aca="false">ROUND(I22*(1-Assumptions!$B$9/4)+J21,0)</f>
-        <v>12</v>
+        <f aca="false">ROUND(I22*(1-Assumptions!$B$10/4)+J21,0)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="J23" s="41" t="n">
         <f aca="false">ROUND(J22*Assumptions!$B$42,0)</f>
-        <v>163200</v>
+        <v>176800</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3080,31 +3080,31 @@
         <v>0</v>
       </c>
       <c r="D27" s="31" t="n">
-        <f aca="false">ROUND(C27*(1-Assumptions!$B$9/4)+D26,0)</f>
+        <f aca="false">ROUND(C27*(1-Assumptions!$B$10/4)+D26,0)</f>
         <v>0</v>
       </c>
       <c r="E27" s="31" t="n">
-        <f aca="false">ROUND(D27*(1-Assumptions!$B$9/4)+E26,0)</f>
+        <f aca="false">ROUND(D27*(1-Assumptions!$B$10/4)+E26,0)</f>
         <v>0</v>
       </c>
       <c r="F27" s="31" t="n">
-        <f aca="false">ROUND(E27*(1-Assumptions!$B$9/4)+F26,0)</f>
+        <f aca="false">ROUND(E27*(1-Assumptions!$B$10/4)+F26,0)</f>
         <v>0</v>
       </c>
       <c r="G27" s="31" t="n">
-        <f aca="false">ROUND(F27*(1-Assumptions!$B$9/4)+G26,0)</f>
+        <f aca="false">ROUND(F27*(1-Assumptions!$B$10/4)+G26,0)</f>
         <v>0</v>
       </c>
       <c r="H27" s="31" t="n">
-        <f aca="false">ROUND(G27*(1-Assumptions!$B$9/4)+H26,0)</f>
+        <f aca="false">ROUND(G27*(1-Assumptions!$B$10/4)+H26,0)</f>
         <v>0</v>
       </c>
       <c r="I27" s="31" t="n">
-        <f aca="false">ROUND(H27*(1-Assumptions!$B$9/4)+I26,0)</f>
+        <f aca="false">ROUND(H27*(1-Assumptions!$B$10/4)+I26,0)</f>
         <v>0</v>
       </c>
       <c r="J27" s="31" t="n">
-        <f aca="false">ROUND(I27*(1-Assumptions!$B$9/4)+J26,0)</f>
+        <f aca="false">ROUND(I27*(1-Assumptions!$B$10/4)+J26,0)</f>
         <v>7</v>
       </c>
     </row>
@@ -3180,27 +3180,27 @@
       </c>
       <c r="E31" s="57" t="n">
         <f aca="false">E7+E12+E17+E22+E27</f>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F31" s="57" t="n">
         <f aca="false">F7+F12+F17+F22+F27</f>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G31" s="57" t="n">
         <f aca="false">G7+G12+G17+G22+G27</f>
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H31" s="57" t="n">
         <f aca="false">H7+H12+H17+H22+H27</f>
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I31" s="57" t="n">
         <f aca="false">I7+I12+I17+I22+I27</f>
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="J31" s="57" t="n">
         <f aca="false">J7+J12+J17+J22+J27</f>
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3220,27 +3220,27 @@
       </c>
       <c r="E32" s="59" t="n">
         <f aca="false">E8+E13+E18+E23+E28</f>
-        <v>116400</v>
+        <v>48500</v>
       </c>
       <c r="F32" s="59" t="n">
         <f aca="false">F8+F13+F18+F23+F28</f>
-        <v>409200</v>
+        <v>292800</v>
       </c>
       <c r="G32" s="59" t="n">
         <f aca="false">G8+G13+G18+G23+G28</f>
-        <v>762200</v>
+        <v>620700</v>
       </c>
       <c r="H32" s="59" t="n">
         <f aca="false">H8+H13+H18+H23+H28</f>
-        <v>1036500</v>
+        <v>910100</v>
       </c>
       <c r="I32" s="59" t="n">
         <f aca="false">I8+I13+I18+I23+I28</f>
-        <v>1333000</v>
+        <v>1246500</v>
       </c>
       <c r="J32" s="59" t="n">
         <f aca="false">J8+J13+J18+J23+J28</f>
-        <v>1658000</v>
+        <v>1637300</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,23 +3263,23 @@
       </c>
       <c r="F33" s="62" t="n">
         <f aca="false">IF(E32=0,"-",(F32-E32)/E32)</f>
-        <v>2.51546391752577</v>
+        <v>5.03711340206186</v>
       </c>
       <c r="G33" s="62" t="n">
         <f aca="false">IF(F32=0,"-",(G32-F32)/F32)</f>
-        <v>0.862658846529814</v>
+        <v>1.11987704918033</v>
       </c>
       <c r="H33" s="62" t="n">
         <f aca="false">IF(G32=0,"-",(H32-G32)/G32)</f>
-        <v>0.359879296772501</v>
+        <v>0.466247784759143</v>
       </c>
       <c r="I33" s="62" t="n">
         <f aca="false">IF(H32=0,"-",(I32-H32)/H32)</f>
-        <v>0.286058851905451</v>
+        <v>0.369629711020767</v>
       </c>
       <c r="J33" s="62" t="n">
         <f aca="false">IF(I32=0,"-",(J32-I32)/I32)</f>
-        <v>0.243810952738185</v>
+        <v>0.313517849979944</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="H34" s="14" t="str">
         <f aca="false">IF(H32&gt;=1000000,"✓ $1M","—")</f>
-        <v>✓ $1M</v>
+        <v>—</v>
       </c>
       <c r="I34" s="14" t="str">
         <f aca="false">IF(I32&gt;=1000000,"✓ $1M","—")</f>
